--- a/BI/TP_BI/D001.xlsx
+++ b/BI/TP_BI/D001.xlsx
@@ -1,15 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_7CF9E86243BE6F2EFF551E95EB923BBCFDD11D9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -187,9 +201,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -233,7 +247,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -256,9 +270,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -296,9 +310,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -333,7 +347,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -368,7 +382,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -541,7 +555,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L390"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -628,9 +642,9 @@
       <c r="K2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="2" t="e">
+      <c r="L2" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41142.368062485068</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -667,9 +681,9 @@
       <c r="K3" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="2" t="e">
+      <c r="L3" s="2">
         <f t="shared" ref="L3:L66" ca="1" si="0">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41599.091794065185</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -706,9 +720,9 @@
       <c r="K4" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="2" t="e">
+      <c r="L4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40317.06884264882</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -745,9 +759,9 @@
       <c r="K5" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="2" t="e">
+      <c r="L5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40845.984359803704</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -784,9 +798,9 @@
       <c r="K6" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="2" t="e">
+      <c r="L6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40363.737428894943</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -823,9 +837,9 @@
       <c r="K7" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="2" t="e">
+      <c r="L7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41543.723785574868</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -862,9 +876,9 @@
       <c r="K8" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="2" t="e">
+      <c r="L8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41739.663873559366</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -901,9 +915,9 @@
       <c r="K9" t="s">
         <v>31</v>
       </c>
-      <c r="L9" s="2" t="e">
+      <c r="L9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42351.238349902662</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -940,9 +954,9 @@
       <c r="K10" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="2" t="e">
+      <c r="L10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41918.314259073763</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -979,9 +993,9 @@
       <c r="K11" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="2" t="e">
+      <c r="L11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41237.705072690806</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -1018,9 +1032,9 @@
       <c r="K12" t="s">
         <v>31</v>
       </c>
-      <c r="L12" s="2" t="e">
+      <c r="L12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42261.90994475261</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1057,9 +1071,9 @@
       <c r="K13" t="s">
         <v>37</v>
       </c>
-      <c r="L13" s="2" t="e">
+      <c r="L13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42009.94237846569</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1096,9 +1110,9 @@
       <c r="K14" t="s">
         <v>14</v>
       </c>
-      <c r="L14" s="2" t="e">
+      <c r="L14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41176.427072434417</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -1135,9 +1149,9 @@
       <c r="K15" t="s">
         <v>37</v>
       </c>
-      <c r="L15" s="2" t="e">
+      <c r="L15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40249.779925785297</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1174,9 +1188,9 @@
       <c r="K16" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="2" t="e">
+      <c r="L16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40895.412324096978</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -1213,9 +1227,9 @@
       <c r="K17" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="2" t="e">
+      <c r="L17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41037.233079435988</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -1252,9 +1266,9 @@
       <c r="K18" t="s">
         <v>31</v>
       </c>
-      <c r="L18" s="2" t="e">
+      <c r="L18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40985.034921179242</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -1291,9 +1305,9 @@
       <c r="K19" t="s">
         <v>14</v>
       </c>
-      <c r="L19" s="2" t="e">
+      <c r="L19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41961.825982691749</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1330,9 +1344,9 @@
       <c r="K20" t="s">
         <v>23</v>
       </c>
-      <c r="L20" s="2" t="e">
+      <c r="L20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41516.06087285492</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1369,9 +1383,9 @@
       <c r="K21" t="s">
         <v>26</v>
       </c>
-      <c r="L21" s="2" t="e">
+      <c r="L21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42213.262118686158</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -1408,9 +1422,9 @@
       <c r="K22" t="s">
         <v>29</v>
       </c>
-      <c r="L22" s="2" t="e">
+      <c r="L22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41785.794488699328</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -1447,9 +1461,9 @@
       <c r="K23" t="s">
         <v>31</v>
       </c>
-      <c r="L23" s="2" t="e">
+      <c r="L23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41349.908208947141</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -1486,9 +1500,9 @@
       <c r="K24" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="2" t="e">
+      <c r="L24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41124.499150176256</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -1525,9 +1539,9 @@
       <c r="K25" t="s">
         <v>26</v>
       </c>
-      <c r="L25" s="2" t="e">
+      <c r="L25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40680.02752509393</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -1564,9 +1578,9 @@
       <c r="K26" t="s">
         <v>26</v>
       </c>
-      <c r="L26" s="2" t="e">
+      <c r="L26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41301.130175689395</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -1603,9 +1617,9 @@
       <c r="K27" t="s">
         <v>14</v>
       </c>
-      <c r="L27" s="2" t="e">
+      <c r="L27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40959.556454960737</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
@@ -1642,9 +1656,9 @@
       <c r="K28" t="s">
         <v>23</v>
       </c>
-      <c r="L28" s="2" t="e">
+      <c r="L28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40641.369356828684</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -1681,9 +1695,9 @@
       <c r="K29" t="s">
         <v>14</v>
       </c>
-      <c r="L29" s="2" t="e">
+      <c r="L29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41512.987546408578</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
@@ -1720,9 +1734,9 @@
       <c r="K30" t="s">
         <v>17</v>
       </c>
-      <c r="L30" s="2" t="e">
+      <c r="L30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42023.288087377419</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
@@ -1759,9 +1773,9 @@
       <c r="K31" t="s">
         <v>17</v>
       </c>
-      <c r="L31" s="2" t="e">
+      <c r="L31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40488.18366186905</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
@@ -1798,9 +1812,9 @@
       <c r="K32" t="s">
         <v>20</v>
       </c>
-      <c r="L32" s="2" t="e">
+      <c r="L32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40851.840412366451</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -1837,9 +1851,9 @@
       <c r="K33" t="s">
         <v>20</v>
       </c>
-      <c r="L33" s="2" t="e">
+      <c r="L33" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42331.186029465207</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -1876,9 +1890,9 @@
       <c r="K34" t="s">
         <v>20</v>
       </c>
-      <c r="L34" s="2" t="e">
+      <c r="L34" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41943.472402589752</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -1915,9 +1929,9 @@
       <c r="K35" t="s">
         <v>31</v>
       </c>
-      <c r="L35" s="2" t="e">
+      <c r="L35" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40461.190110675714</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -1954,9 +1968,9 @@
       <c r="K36" t="s">
         <v>33</v>
       </c>
-      <c r="L36" s="2" t="e">
+      <c r="L36" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41374.394063489213</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -1993,9 +2007,9 @@
       <c r="K37" t="s">
         <v>33</v>
       </c>
-      <c r="L37" s="2" t="e">
+      <c r="L37" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41190.877220336595</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -2032,9 +2046,9 @@
       <c r="K38" t="s">
         <v>23</v>
       </c>
-      <c r="L38" s="2" t="e">
+      <c r="L38" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40745.428509444173</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -2071,9 +2085,9 @@
       <c r="K39" t="s">
         <v>14</v>
       </c>
-      <c r="L39" s="2" t="e">
+      <c r="L39" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42279.32427728115</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -2110,9 +2124,9 @@
       <c r="K40" t="s">
         <v>33</v>
       </c>
-      <c r="L40" s="2" t="e">
+      <c r="L40" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41046.929094088191</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -2149,9 +2163,9 @@
       <c r="K41" t="s">
         <v>37</v>
       </c>
-      <c r="L41" s="2" t="e">
+      <c r="L41" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42195.153523947607</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2188,9 +2202,9 @@
       <c r="K42" t="s">
         <v>23</v>
       </c>
-      <c r="L42" s="2" t="e">
+      <c r="L42" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41589.906080202025</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -2227,9 +2241,9 @@
       <c r="K43" t="s">
         <v>29</v>
       </c>
-      <c r="L43" s="2" t="e">
+      <c r="L43" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41231.232265198698</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -2266,9 +2280,9 @@
       <c r="K44" t="s">
         <v>14</v>
       </c>
-      <c r="L44" s="2" t="e">
+      <c r="L44" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42172.600216733859</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -2305,9 +2319,9 @@
       <c r="K45" t="s">
         <v>31</v>
       </c>
-      <c r="L45" s="2" t="e">
+      <c r="L45" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40450.725720907154</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -2344,9 +2358,9 @@
       <c r="K46" t="s">
         <v>14</v>
       </c>
-      <c r="L46" s="2" t="e">
+      <c r="L46" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41620.984985949661</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -2383,9 +2397,9 @@
       <c r="K47" t="s">
         <v>31</v>
       </c>
-      <c r="L47" s="2" t="e">
+      <c r="L47" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41084.669639298743</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -2422,9 +2436,9 @@
       <c r="K48" t="s">
         <v>14</v>
       </c>
-      <c r="L48" s="2" t="e">
+      <c r="L48" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40514.315070394237</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -2461,9 +2475,9 @@
       <c r="K49" t="s">
         <v>37</v>
       </c>
-      <c r="L49" s="2" t="e">
+      <c r="L49" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41412.143269722757</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -2500,9 +2514,9 @@
       <c r="K50" t="s">
         <v>31</v>
       </c>
-      <c r="L50" s="2" t="e">
+      <c r="L50" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41927.326204326295</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -2539,9 +2553,9 @@
       <c r="K51" t="s">
         <v>23</v>
       </c>
-      <c r="L51" s="2" t="e">
+      <c r="L51" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40292.856094975818</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -2578,9 +2592,9 @@
       <c r="K52" t="s">
         <v>17</v>
       </c>
-      <c r="L52" s="2" t="e">
+      <c r="L52" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40914.138205076495</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -2617,9 +2631,9 @@
       <c r="K53" t="s">
         <v>37</v>
       </c>
-      <c r="L53" s="2" t="e">
+      <c r="L53" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40236.84198773095</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -2656,9 +2670,9 @@
       <c r="K54" t="s">
         <v>37</v>
       </c>
-      <c r="L54" s="2" t="e">
+      <c r="L54" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40964.924438994778</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -2695,9 +2709,9 @@
       <c r="K55" t="s">
         <v>33</v>
       </c>
-      <c r="L55" s="2" t="e">
+      <c r="L55" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40326.984363904558</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -2734,9 +2748,9 @@
       <c r="K56" t="s">
         <v>29</v>
       </c>
-      <c r="L56" s="2" t="e">
+      <c r="L56" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41318.527703286993</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -2773,9 +2787,9 @@
       <c r="K57" t="s">
         <v>14</v>
       </c>
-      <c r="L57" s="2" t="e">
+      <c r="L57" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41007.172723735246</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -2812,9 +2826,9 @@
       <c r="K58" t="s">
         <v>33</v>
       </c>
-      <c r="L58" s="2" t="e">
+      <c r="L58" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42071.251677359498</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -2851,9 +2865,9 @@
       <c r="K59" t="s">
         <v>54</v>
       </c>
-      <c r="L59" s="2" t="e">
+      <c r="L59" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41803.913075265395</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
@@ -2890,9 +2904,9 @@
       <c r="K60" t="s">
         <v>29</v>
       </c>
-      <c r="L60" s="2" t="e">
+      <c r="L60" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40606.612975483768</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -2929,9 +2943,9 @@
       <c r="K61" t="s">
         <v>26</v>
       </c>
-      <c r="L61" s="2" t="e">
+      <c r="L61" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40565.049533310608</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
@@ -2968,9 +2982,9 @@
       <c r="K62" t="s">
         <v>31</v>
       </c>
-      <c r="L62" s="2" t="e">
+      <c r="L62" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40661.821782736253</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -3007,9 +3021,9 @@
       <c r="K63" t="s">
         <v>29</v>
       </c>
-      <c r="L63" s="2" t="e">
+      <c r="L63" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>41600.926252321893</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
@@ -3046,9 +3060,9 @@
       <c r="K64" t="s">
         <v>31</v>
       </c>
-      <c r="L64" s="2" t="e">
+      <c r="L64" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>40906.166507465379</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
@@ -3085,9 +3099,9 @@
       <c r="K65" t="s">
         <v>20</v>
       </c>
-      <c r="L65" s="2" t="e">
+      <c r="L65" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42030.929957905508</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
@@ -3124,9 +3138,9 @@
       <c r="K66" t="s">
         <v>26</v>
       </c>
-      <c r="L66" s="2" t="e">
+      <c r="L66" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>42206.888474253217</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
@@ -3163,9 +3177,9 @@
       <c r="K67" t="s">
         <v>54</v>
       </c>
-      <c r="L67" s="2" t="e">
+      <c r="L67" s="2">
         <f t="shared" ref="L67:L130" ca="1" si="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41128.850765060859</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
@@ -3202,9 +3216,9 @@
       <c r="K68" t="s">
         <v>17</v>
       </c>
-      <c r="L68" s="2" t="e">
+      <c r="L68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41574.612051757198</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
@@ -3241,9 +3255,9 @@
       <c r="K69" t="s">
         <v>54</v>
       </c>
-      <c r="L69" s="2" t="e">
+      <c r="L69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41144.778572802898</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
@@ -3280,9 +3294,9 @@
       <c r="K70" t="s">
         <v>20</v>
       </c>
-      <c r="L70" s="2" t="e">
+      <c r="L70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42284.673115946272</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
@@ -3319,9 +3333,9 @@
       <c r="K71" t="s">
         <v>31</v>
       </c>
-      <c r="L71" s="2" t="e">
+      <c r="L71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42187.920895335919</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -3358,9 +3372,9 @@
       <c r="K72" t="s">
         <v>26</v>
       </c>
-      <c r="L72" s="2" t="e">
+      <c r="L72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41715.726593612679</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -3397,9 +3411,9 @@
       <c r="K73" t="s">
         <v>29</v>
       </c>
-      <c r="L73" s="2" t="e">
+      <c r="L73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41582.986974977997</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
@@ -3436,9 +3450,9 @@
       <c r="K74" t="s">
         <v>17</v>
       </c>
-      <c r="L74" s="2" t="e">
+      <c r="L74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41034.417055535661</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
@@ -3475,9 +3489,9 @@
       <c r="K75" t="s">
         <v>29</v>
       </c>
-      <c r="L75" s="2" t="e">
+      <c r="L75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41010.704333118381</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
@@ -3514,9 +3528,9 @@
       <c r="K76" t="s">
         <v>14</v>
       </c>
-      <c r="L76" s="2" t="e">
+      <c r="L76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42150.48529943527</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
@@ -3553,9 +3567,9 @@
       <c r="K77" t="s">
         <v>14</v>
       </c>
-      <c r="L77" s="2" t="e">
+      <c r="L77" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40932.903415794826</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
@@ -3592,9 +3606,9 @@
       <c r="K78" t="s">
         <v>23</v>
       </c>
-      <c r="L78" s="2" t="e">
+      <c r="L78" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41206.01256033656</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
@@ -3631,9 +3645,9 @@
       <c r="K79" t="s">
         <v>54</v>
       </c>
-      <c r="L79" s="2" t="e">
+      <c r="L79" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41064.789709214747</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
@@ -3670,9 +3684,9 @@
       <c r="K80" t="s">
         <v>54</v>
       </c>
-      <c r="L80" s="2" t="e">
+      <c r="L80" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42215.207636712272</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
@@ -3709,9 +3723,9 @@
       <c r="K81" t="s">
         <v>31</v>
       </c>
-      <c r="L81" s="2" t="e">
+      <c r="L81" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41789.458913474999</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
@@ -3748,9 +3762,9 @@
       <c r="K82" t="s">
         <v>33</v>
       </c>
-      <c r="L82" s="2" t="e">
+      <c r="L82" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40945.541124050986</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
@@ -3787,9 +3801,9 @@
       <c r="K83" t="s">
         <v>31</v>
       </c>
-      <c r="L83" s="2" t="e">
+      <c r="L83" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42299.835185848337</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
@@ -3826,9 +3840,9 @@
       <c r="K84" t="s">
         <v>23</v>
       </c>
-      <c r="L84" s="2" t="e">
+      <c r="L84" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40572.608729862477</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
@@ -3865,9 +3879,9 @@
       <c r="K85" t="s">
         <v>17</v>
       </c>
-      <c r="L85" s="2" t="e">
+      <c r="L85" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40507.991181282421</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
@@ -3904,9 +3918,9 @@
       <c r="K86" t="s">
         <v>54</v>
       </c>
-      <c r="L86" s="2" t="e">
+      <c r="L86" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40497.859035072928</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
@@ -3943,9 +3957,9 @@
       <c r="K87" t="s">
         <v>37</v>
       </c>
-      <c r="L87" s="2" t="e">
+      <c r="L87" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40376.86252112066</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
@@ -3982,9 +3996,9 @@
       <c r="K88" t="s">
         <v>31</v>
       </c>
-      <c r="L88" s="2" t="e">
+      <c r="L88" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41638.946124885733</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
@@ -4021,9 +4035,9 @@
       <c r="K89" t="s">
         <v>54</v>
       </c>
-      <c r="L89" s="2" t="e">
+      <c r="L89" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41267.924464218704</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
@@ -4060,9 +4074,9 @@
       <c r="K90" t="s">
         <v>29</v>
       </c>
-      <c r="L90" s="2" t="e">
+      <c r="L90" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41096.174569798779</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
@@ -4099,9 +4113,9 @@
       <c r="K91" t="s">
         <v>23</v>
       </c>
-      <c r="L91" s="2" t="e">
+      <c r="L91" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40810.624825603343</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
@@ -4138,9 +4152,9 @@
       <c r="K92" t="s">
         <v>26</v>
       </c>
-      <c r="L92" s="2" t="e">
+      <c r="L92" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40650.079240734318</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
@@ -4177,9 +4191,9 @@
       <c r="K93" t="s">
         <v>31</v>
       </c>
-      <c r="L93" s="2" t="e">
+      <c r="L93" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42317.806228253248</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
@@ -4216,9 +4230,9 @@
       <c r="K94" t="s">
         <v>23</v>
       </c>
-      <c r="L94" s="2" t="e">
+      <c r="L94" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41608.245550259613</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
@@ -4255,9 +4269,9 @@
       <c r="K95" t="s">
         <v>29</v>
       </c>
-      <c r="L95" s="2" t="e">
+      <c r="L95" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40577.321608115097</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
@@ -4294,9 +4308,9 @@
       <c r="K96" t="s">
         <v>17</v>
       </c>
-      <c r="L96" s="2" t="e">
+      <c r="L96" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40970.434684807267</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
@@ -4333,9 +4347,9 @@
       <c r="K97" t="s">
         <v>29</v>
       </c>
-      <c r="L97" s="2" t="e">
+      <c r="L97" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41894.786880911124</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -4372,9 +4386,9 @@
       <c r="K98" t="s">
         <v>31</v>
       </c>
-      <c r="L98" s="2" t="e">
+      <c r="L98" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42022.554859489799</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
@@ -4411,9 +4425,9 @@
       <c r="K99" t="s">
         <v>20</v>
       </c>
-      <c r="L99" s="2" t="e">
+      <c r="L99" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40330.865083701501</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
@@ -4450,9 +4464,9 @@
       <c r="K100" t="s">
         <v>37</v>
       </c>
-      <c r="L100" s="2" t="e">
+      <c r="L100" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41757.735059426457</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
@@ -4489,9 +4503,9 @@
       <c r="K101" t="s">
         <v>20</v>
       </c>
-      <c r="L101" s="2" t="e">
+      <c r="L101" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41907.518710716526</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
@@ -4528,9 +4542,9 @@
       <c r="K102" t="s">
         <v>37</v>
       </c>
-      <c r="L102" s="2" t="e">
+      <c r="L102" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42019.928437117087</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
@@ -4567,9 +4581,9 @@
       <c r="K103" t="s">
         <v>31</v>
       </c>
-      <c r="L103" s="2" t="e">
+      <c r="L103" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42044.043273337331</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
@@ -4606,9 +4620,9 @@
       <c r="K104" t="s">
         <v>20</v>
       </c>
-      <c r="L104" s="2" t="e">
+      <c r="L104" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41384.789523562315</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
@@ -4645,9 +4659,9 @@
       <c r="K105" t="s">
         <v>26</v>
       </c>
-      <c r="L105" s="2" t="e">
+      <c r="L105" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41033.457342237918</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
@@ -4684,9 +4698,9 @@
       <c r="K106" t="s">
         <v>31</v>
       </c>
-      <c r="L106" s="2" t="e">
+      <c r="L106" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41472.833730651495</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
@@ -4723,9 +4737,9 @@
       <c r="K107" t="s">
         <v>14</v>
       </c>
-      <c r="L107" s="2" t="e">
+      <c r="L107" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40809.991879448142</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
@@ -4762,9 +4776,9 @@
       <c r="K108" t="s">
         <v>37</v>
       </c>
-      <c r="L108" s="2" t="e">
+      <c r="L108" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41859.465789870068</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
@@ -4801,9 +4815,9 @@
       <c r="K109" t="s">
         <v>29</v>
       </c>
-      <c r="L109" s="2" t="e">
+      <c r="L109" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41411.840405047187</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -4840,9 +4854,9 @@
       <c r="K110" t="s">
         <v>20</v>
       </c>
-      <c r="L110" s="2" t="e">
+      <c r="L110" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41545.604462709642</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
@@ -4879,9 +4893,9 @@
       <c r="K111" t="s">
         <v>29</v>
       </c>
-      <c r="L111" s="2" t="e">
+      <c r="L111" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41412.895961435846</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
@@ -4918,9 +4932,9 @@
       <c r="K112" t="s">
         <v>37</v>
       </c>
-      <c r="L112" s="2" t="e">
+      <c r="L112" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40542.206437864545</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
@@ -4957,9 +4971,9 @@
       <c r="K113" t="s">
         <v>29</v>
       </c>
-      <c r="L113" s="2" t="e">
+      <c r="L113" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40383.960877323931</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
@@ -4996,9 +5010,9 @@
       <c r="K114" t="s">
         <v>29</v>
       </c>
-      <c r="L114" s="2" t="e">
+      <c r="L114" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40856.87628094267</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
@@ -5035,9 +5049,9 @@
       <c r="K115" t="s">
         <v>31</v>
       </c>
-      <c r="L115" s="2" t="e">
+      <c r="L115" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40851.269270052595</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
@@ -5074,9 +5088,9 @@
       <c r="K116" t="s">
         <v>29</v>
       </c>
-      <c r="L116" s="2" t="e">
+      <c r="L116" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41114.249947937205</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
@@ -5113,9 +5127,9 @@
       <c r="K117" t="s">
         <v>31</v>
       </c>
-      <c r="L117" s="2" t="e">
+      <c r="L117" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40400.274050220112</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
@@ -5152,9 +5166,9 @@
       <c r="K118" t="s">
         <v>31</v>
       </c>
-      <c r="L118" s="2" t="e">
+      <c r="L118" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>42340.15567022613</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
@@ -5191,9 +5205,9 @@
       <c r="K119" t="s">
         <v>31</v>
       </c>
-      <c r="L119" s="2" t="e">
+      <c r="L119" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41992.882768809817</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
@@ -5230,9 +5244,9 @@
       <c r="K120" t="s">
         <v>20</v>
       </c>
-      <c r="L120" s="2" t="e">
+      <c r="L120" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41089.75777711461</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
@@ -5269,9 +5283,9 @@
       <c r="K121" t="s">
         <v>33</v>
       </c>
-      <c r="L121" s="2" t="e">
+      <c r="L121" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41986.08705025442</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
@@ -5308,9 +5322,9 @@
       <c r="K122" t="s">
         <v>29</v>
       </c>
-      <c r="L122" s="2" t="e">
+      <c r="L122" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40929.716545240422</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
@@ -5347,9 +5361,9 @@
       <c r="K123" t="s">
         <v>23</v>
       </c>
-      <c r="L123" s="2" t="e">
+      <c r="L123" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41317.719030421351</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
@@ -5386,9 +5400,9 @@
       <c r="K124" t="s">
         <v>17</v>
       </c>
-      <c r="L124" s="2" t="e">
+      <c r="L124" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40655.591218689406</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
@@ -5425,9 +5439,9 @@
       <c r="K125" t="s">
         <v>33</v>
       </c>
-      <c r="L125" s="2" t="e">
+      <c r="L125" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40743.490363448989</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
@@ -5464,9 +5478,9 @@
       <c r="K126" t="s">
         <v>26</v>
       </c>
-      <c r="L126" s="2" t="e">
+      <c r="L126" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41192.933874775597</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
@@ -5503,9 +5517,9 @@
       <c r="K127" t="s">
         <v>23</v>
       </c>
-      <c r="L127" s="2" t="e">
+      <c r="L127" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40600.631721181948</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
@@ -5542,9 +5556,9 @@
       <c r="K128" t="s">
         <v>26</v>
       </c>
-      <c r="L128" s="2" t="e">
+      <c r="L128" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>40475.408473139782</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
@@ -5581,9 +5595,9 @@
       <c r="K129" t="s">
         <v>33</v>
       </c>
-      <c r="L129" s="2" t="e">
+      <c r="L129" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41800.473636380426</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
@@ -5620,9 +5634,9 @@
       <c r="K130" t="s">
         <v>54</v>
       </c>
-      <c r="L130" s="2" t="e">
+      <c r="L130" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
+        <v>41497.463985827126</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
@@ -5659,9 +5673,9 @@
       <c r="K131" t="s">
         <v>33</v>
       </c>
-      <c r="L131" s="2" t="e">
+      <c r="L131" s="2">
         <f t="shared" ref="L131:L194" ca="1" si="2">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41520.685328268541</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -5698,9 +5712,9 @@
       <c r="K132" t="s">
         <v>33</v>
       </c>
-      <c r="L132" s="2" t="e">
+      <c r="L132" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40857.89920478416</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
@@ -5737,9 +5751,9 @@
       <c r="K133" t="s">
         <v>14</v>
       </c>
-      <c r="L133" s="2" t="e">
+      <c r="L133" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41438.244087608</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
@@ -5776,9 +5790,9 @@
       <c r="K134" t="s">
         <v>37</v>
       </c>
-      <c r="L134" s="2" t="e">
+      <c r="L134" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41652.865853221134</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
@@ -5815,9 +5829,9 @@
       <c r="K135" t="s">
         <v>37</v>
       </c>
-      <c r="L135" s="2" t="e">
+      <c r="L135" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41400.536238006694</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
@@ -5854,9 +5868,9 @@
       <c r="K136" t="s">
         <v>14</v>
       </c>
-      <c r="L136" s="2" t="e">
+      <c r="L136" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40334.232094012223</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
@@ -5893,9 +5907,9 @@
       <c r="K137" t="s">
         <v>31</v>
       </c>
-      <c r="L137" s="2" t="e">
+      <c r="L137" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41078.370331786806</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
@@ -5932,9 +5946,9 @@
       <c r="K138" t="s">
         <v>31</v>
       </c>
-      <c r="L138" s="2" t="e">
+      <c r="L138" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41803.147104703225</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
@@ -5971,9 +5985,9 @@
       <c r="K139" t="s">
         <v>23</v>
       </c>
-      <c r="L139" s="2" t="e">
+      <c r="L139" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41967.592026866303</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
@@ -6010,9 +6024,9 @@
       <c r="K140" t="s">
         <v>17</v>
       </c>
-      <c r="L140" s="2" t="e">
+      <c r="L140" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41247.912316998088</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
@@ -6049,9 +6063,9 @@
       <c r="K141" t="s">
         <v>23</v>
       </c>
-      <c r="L141" s="2" t="e">
+      <c r="L141" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41457.708280787148</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
@@ -6088,9 +6102,9 @@
       <c r="K142" t="s">
         <v>31</v>
       </c>
-      <c r="L142" s="2" t="e">
+      <c r="L142" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40379.956265283203</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
@@ -6127,9 +6141,9 @@
       <c r="K143" t="s">
         <v>29</v>
       </c>
-      <c r="L143" s="2" t="e">
+      <c r="L143" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41507.610749924024</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
@@ -6166,9 +6180,9 @@
       <c r="K144" t="s">
         <v>23</v>
       </c>
-      <c r="L144" s="2" t="e">
+      <c r="L144" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40895.734918320508</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
@@ -6205,9 +6219,9 @@
       <c r="K145" t="s">
         <v>20</v>
       </c>
-      <c r="L145" s="2" t="e">
+      <c r="L145" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40803.507884652383</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
@@ -6244,9 +6258,9 @@
       <c r="K146" t="s">
         <v>33</v>
       </c>
-      <c r="L146" s="2" t="e">
+      <c r="L146" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40411.366276635024</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
@@ -6283,9 +6297,9 @@
       <c r="K147" t="s">
         <v>54</v>
       </c>
-      <c r="L147" s="2" t="e">
+      <c r="L147" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41945.450398826193</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
@@ -6322,9 +6336,9 @@
       <c r="K148" t="s">
         <v>29</v>
       </c>
-      <c r="L148" s="2" t="e">
+      <c r="L148" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42261.576238346635</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
@@ -6361,9 +6375,9 @@
       <c r="K149" t="s">
         <v>17</v>
       </c>
-      <c r="L149" s="2" t="e">
+      <c r="L149" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40871.645901979537</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
@@ -6400,9 +6414,9 @@
       <c r="K150" t="s">
         <v>33</v>
       </c>
-      <c r="L150" s="2" t="e">
+      <c r="L150" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42299.828913170735</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
@@ -6439,9 +6453,9 @@
       <c r="K151" t="s">
         <v>14</v>
       </c>
-      <c r="L151" s="2" t="e">
+      <c r="L151" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41492.322704372593</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
@@ -6478,9 +6492,9 @@
       <c r="K152" t="s">
         <v>33</v>
       </c>
-      <c r="L152" s="2" t="e">
+      <c r="L152" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41508.373871615215</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
@@ -6517,9 +6531,9 @@
       <c r="K153" t="s">
         <v>26</v>
       </c>
-      <c r="L153" s="2" t="e">
+      <c r="L153" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40737.045973067674</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
@@ -6556,9 +6570,9 @@
       <c r="K154" t="s">
         <v>26</v>
       </c>
-      <c r="L154" s="2" t="e">
+      <c r="L154" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40632.112689873196</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
@@ -6595,9 +6609,9 @@
       <c r="K155" t="s">
         <v>37</v>
       </c>
-      <c r="L155" s="2" t="e">
+      <c r="L155" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40561.199820119735</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
@@ -6634,9 +6648,9 @@
       <c r="K156" t="s">
         <v>54</v>
       </c>
-      <c r="L156" s="2" t="e">
+      <c r="L156" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42272.957021532209</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
@@ -6673,9 +6687,9 @@
       <c r="K157" t="s">
         <v>17</v>
       </c>
-      <c r="L157" s="2" t="e">
+      <c r="L157" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41197.462478837901</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
@@ -6712,9 +6726,9 @@
       <c r="K158" t="s">
         <v>54</v>
       </c>
-      <c r="L158" s="2" t="e">
+      <c r="L158" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41962.084533648078</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
@@ -6751,9 +6765,9 @@
       <c r="K159" t="s">
         <v>54</v>
       </c>
-      <c r="L159" s="2" t="e">
+      <c r="L159" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41027.795371345528</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
@@ -6790,9 +6804,9 @@
       <c r="K160" t="s">
         <v>33</v>
       </c>
-      <c r="L160" s="2" t="e">
+      <c r="L160" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42114.529359952576</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
@@ -6829,9 +6843,9 @@
       <c r="K161" t="s">
         <v>54</v>
       </c>
-      <c r="L161" s="2" t="e">
+      <c r="L161" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41422.992444050797</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
@@ -6868,9 +6882,9 @@
       <c r="K162" t="s">
         <v>17</v>
       </c>
-      <c r="L162" s="2" t="e">
+      <c r="L162" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42085.734264095554</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
@@ -6907,9 +6921,9 @@
       <c r="K163" t="s">
         <v>17</v>
       </c>
-      <c r="L163" s="2" t="e">
+      <c r="L163" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42153.466531633603</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
@@ -6946,9 +6960,9 @@
       <c r="K164" t="s">
         <v>31</v>
       </c>
-      <c r="L164" s="2" t="e">
+      <c r="L164" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42042.495067958451</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
@@ -6985,9 +6999,9 @@
       <c r="K165" t="s">
         <v>26</v>
       </c>
-      <c r="L165" s="2" t="e">
+      <c r="L165" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40807.314816708276</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
@@ -7024,9 +7038,9 @@
       <c r="K166" t="s">
         <v>26</v>
       </c>
-      <c r="L166" s="2" t="e">
+      <c r="L166" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41946.427286731669</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
@@ -7063,9 +7077,9 @@
       <c r="K167" t="s">
         <v>26</v>
       </c>
-      <c r="L167" s="2" t="e">
+      <c r="L167" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40402.350074665883</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
@@ -7102,9 +7116,9 @@
       <c r="K168" t="s">
         <v>17</v>
       </c>
-      <c r="L168" s="2" t="e">
+      <c r="L168" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42311.389218006239</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
@@ -7141,9 +7155,9 @@
       <c r="K169" t="s">
         <v>14</v>
       </c>
-      <c r="L169" s="2" t="e">
+      <c r="L169" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42175.22489706082</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
@@ -7180,9 +7194,9 @@
       <c r="K170" t="s">
         <v>33</v>
       </c>
-      <c r="L170" s="2" t="e">
+      <c r="L170" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40270.700386828968</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
@@ -7219,9 +7233,9 @@
       <c r="K171" t="s">
         <v>54</v>
       </c>
-      <c r="L171" s="2" t="e">
+      <c r="L171" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41029.656760450991</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
@@ -7258,9 +7272,9 @@
       <c r="K172" t="s">
         <v>26</v>
       </c>
-      <c r="L172" s="2" t="e">
+      <c r="L172" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40193.708481233123</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
@@ -7297,9 +7311,9 @@
       <c r="K173" t="s">
         <v>17</v>
       </c>
-      <c r="L173" s="2" t="e">
+      <c r="L173" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41728.104405909733</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
@@ -7336,9 +7350,9 @@
       <c r="K174" t="s">
         <v>20</v>
       </c>
-      <c r="L174" s="2" t="e">
+      <c r="L174" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42216.911620222738</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
@@ -7375,9 +7389,9 @@
       <c r="K175" t="s">
         <v>23</v>
       </c>
-      <c r="L175" s="2" t="e">
+      <c r="L175" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40435.491548468839</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
@@ -7414,9 +7428,9 @@
       <c r="K176" t="s">
         <v>54</v>
       </c>
-      <c r="L176" s="2" t="e">
+      <c r="L176" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41815.264925181262</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
@@ -7453,9 +7467,9 @@
       <c r="K177" t="s">
         <v>33</v>
       </c>
-      <c r="L177" s="2" t="e">
+      <c r="L177" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40922.197815155618</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
@@ -7492,9 +7506,9 @@
       <c r="K178" t="s">
         <v>17</v>
       </c>
-      <c r="L178" s="2" t="e">
+      <c r="L178" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41857.278478244836</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
@@ -7531,9 +7545,9 @@
       <c r="K179" t="s">
         <v>20</v>
       </c>
-      <c r="L179" s="2" t="e">
+      <c r="L179" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41951.361114824678</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
@@ -7570,9 +7584,9 @@
       <c r="K180" t="s">
         <v>26</v>
       </c>
-      <c r="L180" s="2" t="e">
+      <c r="L180" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41911.829925988473</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
@@ -7609,9 +7623,9 @@
       <c r="K181" t="s">
         <v>20</v>
       </c>
-      <c r="L181" s="2" t="e">
+      <c r="L181" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41995.489020376022</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
@@ -7648,9 +7662,9 @@
       <c r="K182" t="s">
         <v>20</v>
       </c>
-      <c r="L182" s="2" t="e">
+      <c r="L182" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40842.147450617136</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
@@ -7687,9 +7701,9 @@
       <c r="K183" t="s">
         <v>33</v>
       </c>
-      <c r="L183" s="2" t="e">
+      <c r="L183" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>42348.4422673933</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
@@ -7726,9 +7740,9 @@
       <c r="K184" t="s">
         <v>20</v>
       </c>
-      <c r="L184" s="2" t="e">
+      <c r="L184" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41423.786982817524</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
@@ -7765,9 +7779,9 @@
       <c r="K185" t="s">
         <v>23</v>
       </c>
-      <c r="L185" s="2" t="e">
+      <c r="L185" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40922.750232003782</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
@@ -7804,9 +7818,9 @@
       <c r="K186" t="s">
         <v>29</v>
       </c>
-      <c r="L186" s="2" t="e">
+      <c r="L186" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41368.294550328072</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
@@ -7843,9 +7857,9 @@
       <c r="K187" t="s">
         <v>20</v>
       </c>
-      <c r="L187" s="2" t="e">
+      <c r="L187" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41258.808399295754</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
@@ -7882,9 +7896,9 @@
       <c r="K188" t="s">
         <v>37</v>
       </c>
-      <c r="L188" s="2" t="e">
+      <c r="L188" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41943.7316439602</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
@@ -7921,9 +7935,9 @@
       <c r="K189" t="s">
         <v>29</v>
       </c>
-      <c r="L189" s="2" t="e">
+      <c r="L189" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40575.444113632686</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
@@ -7960,9 +7974,9 @@
       <c r="K190" t="s">
         <v>54</v>
       </c>
-      <c r="L190" s="2" t="e">
+      <c r="L190" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41460.696877636721</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
@@ -7999,9 +8013,9 @@
       <c r="K191" t="s">
         <v>33</v>
       </c>
-      <c r="L191" s="2" t="e">
+      <c r="L191" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41245.734078880807</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
@@ -8038,9 +8052,9 @@
       <c r="K192" t="s">
         <v>23</v>
       </c>
-      <c r="L192" s="2" t="e">
+      <c r="L192" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41515.56803321703</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
@@ -8077,9 +8091,9 @@
       <c r="K193" t="s">
         <v>31</v>
       </c>
-      <c r="L193" s="2" t="e">
+      <c r="L193" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>40770.098861237268</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
@@ -8116,9 +8130,9 @@
       <c r="K194" t="s">
         <v>37</v>
       </c>
-      <c r="L194" s="2" t="e">
+      <c r="L194" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>#VALUE!</v>
+        <v>41981.300347912191</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
@@ -8155,9 +8169,9 @@
       <c r="K195" t="s">
         <v>54</v>
       </c>
-      <c r="L195" s="2" t="e">
+      <c r="L195" s="2">
         <f t="shared" ref="L195:L258" ca="1" si="3">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41285.280560556064</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
@@ -8194,9 +8208,9 @@
       <c r="K196" t="s">
         <v>17</v>
       </c>
-      <c r="L196" s="2" t="e">
+      <c r="L196" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40677.388333099414</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
@@ -8233,9 +8247,9 @@
       <c r="K197" t="s">
         <v>33</v>
       </c>
-      <c r="L197" s="2" t="e">
+      <c r="L197" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40288.363615288989</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
@@ -8272,9 +8286,9 @@
       <c r="K198" t="s">
         <v>37</v>
       </c>
-      <c r="L198" s="2" t="e">
+      <c r="L198" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40676.752955835829</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
@@ -8311,9 +8325,9 @@
       <c r="K199" t="s">
         <v>20</v>
       </c>
-      <c r="L199" s="2" t="e">
+      <c r="L199" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40986.950460214059</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
@@ -8350,9 +8364,9 @@
       <c r="K200" t="s">
         <v>33</v>
       </c>
-      <c r="L200" s="2" t="e">
+      <c r="L200" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42246.961671185469</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
@@ -8389,9 +8403,9 @@
       <c r="K201" t="s">
         <v>29</v>
       </c>
-      <c r="L201" s="2" t="e">
+      <c r="L201" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42306.464958656616</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
@@ -8428,9 +8442,9 @@
       <c r="K202" t="s">
         <v>37</v>
       </c>
-      <c r="L202" s="2" t="e">
+      <c r="L202" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41749.974002160423</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
@@ -8467,9 +8481,9 @@
       <c r="K203" t="s">
         <v>29</v>
       </c>
-      <c r="L203" s="2" t="e">
+      <c r="L203" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42013.630603396283</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.3">
@@ -8506,9 +8520,9 @@
       <c r="K204" t="s">
         <v>31</v>
       </c>
-      <c r="L204" s="2" t="e">
+      <c r="L204" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40607.164336421913</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.3">
@@ -8545,9 +8559,9 @@
       <c r="K205" t="s">
         <v>26</v>
       </c>
-      <c r="L205" s="2" t="e">
+      <c r="L205" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40530.068864668072</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
@@ -8584,9 +8598,9 @@
       <c r="K206" t="s">
         <v>23</v>
       </c>
-      <c r="L206" s="2" t="e">
+      <c r="L206" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41563.79945318096</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
@@ -8623,9 +8637,9 @@
       <c r="K207" t="s">
         <v>37</v>
       </c>
-      <c r="L207" s="2" t="e">
+      <c r="L207" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42034.426760430695</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.3">
@@ -8662,9 +8676,9 @@
       <c r="K208" t="s">
         <v>14</v>
       </c>
-      <c r="L208" s="2" t="e">
+      <c r="L208" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42349.90435023488</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.3">
@@ -8701,9 +8715,9 @@
       <c r="K209" t="s">
         <v>26</v>
       </c>
-      <c r="L209" s="2" t="e">
+      <c r="L209" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41396.30700494803</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.3">
@@ -8740,9 +8754,9 @@
       <c r="K210" t="s">
         <v>37</v>
       </c>
-      <c r="L210" s="2" t="e">
+      <c r="L210" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41369.217277690266</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
@@ -8779,9 +8793,9 @@
       <c r="K211" t="s">
         <v>54</v>
       </c>
-      <c r="L211" s="2" t="e">
+      <c r="L211" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40225.026143432806</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
@@ -8818,9 +8832,9 @@
       <c r="K212" t="s">
         <v>54</v>
       </c>
-      <c r="L212" s="2" t="e">
+      <c r="L212" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42062.61594610077</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.3">
@@ -8857,9 +8871,9 @@
       <c r="K213" t="s">
         <v>14</v>
       </c>
-      <c r="L213" s="2" t="e">
+      <c r="L213" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40259.516888340244</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.3">
@@ -8896,9 +8910,9 @@
       <c r="K214" t="s">
         <v>17</v>
       </c>
-      <c r="L214" s="2" t="e">
+      <c r="L214" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41184.744297432473</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.3">
@@ -8935,9 +8949,9 @@
       <c r="K215" t="s">
         <v>23</v>
       </c>
-      <c r="L215" s="2" t="e">
+      <c r="L215" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41329.272269370667</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.3">
@@ -8974,9 +8988,9 @@
       <c r="K216" t="s">
         <v>54</v>
       </c>
-      <c r="L216" s="2" t="e">
+      <c r="L216" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40965.397235608594</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.3">
@@ -9013,9 +9027,9 @@
       <c r="K217" t="s">
         <v>54</v>
       </c>
-      <c r="L217" s="2" t="e">
+      <c r="L217" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40255.672219257918</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.3">
@@ -9052,9 +9066,9 @@
       <c r="K218" t="s">
         <v>23</v>
       </c>
-      <c r="L218" s="2" t="e">
+      <c r="L218" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42330.363384285767</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.3">
@@ -9091,9 +9105,9 @@
       <c r="K219" t="s">
         <v>33</v>
       </c>
-      <c r="L219" s="2" t="e">
+      <c r="L219" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41280.323786640547</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.3">
@@ -9130,9 +9144,9 @@
       <c r="K220" t="s">
         <v>33</v>
       </c>
-      <c r="L220" s="2" t="e">
+      <c r="L220" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41125.649714419793</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.3">
@@ -9169,9 +9183,9 @@
       <c r="K221" t="s">
         <v>54</v>
       </c>
-      <c r="L221" s="2" t="e">
+      <c r="L221" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40264.352230197946</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.3">
@@ -9208,9 +9222,9 @@
       <c r="K222" t="s">
         <v>23</v>
       </c>
-      <c r="L222" s="2" t="e">
+      <c r="L222" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41794.638227592077</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.3">
@@ -9247,9 +9261,9 @@
       <c r="K223" t="s">
         <v>17</v>
       </c>
-      <c r="L223" s="2" t="e">
+      <c r="L223" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40439.778080206685</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.3">
@@ -9286,9 +9300,9 @@
       <c r="K224" t="s">
         <v>26</v>
       </c>
-      <c r="L224" s="2" t="e">
+      <c r="L224" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41542.505372457068</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.3">
@@ -9325,9 +9339,9 @@
       <c r="K225" t="s">
         <v>20</v>
       </c>
-      <c r="L225" s="2" t="e">
+      <c r="L225" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40676.891018581977</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.3">
@@ -9364,9 +9378,9 @@
       <c r="K226" t="s">
         <v>20</v>
       </c>
-      <c r="L226" s="2" t="e">
+      <c r="L226" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41155.357132801437</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.3">
@@ -9403,9 +9417,9 @@
       <c r="K227" t="s">
         <v>37</v>
       </c>
-      <c r="L227" s="2" t="e">
+      <c r="L227" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41484.883756398835</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.3">
@@ -9442,9 +9456,9 @@
       <c r="K228" t="s">
         <v>37</v>
       </c>
-      <c r="L228" s="2" t="e">
+      <c r="L228" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40603.846800135187</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.3">
@@ -9481,9 +9495,9 @@
       <c r="K229" t="s">
         <v>31</v>
       </c>
-      <c r="L229" s="2" t="e">
+      <c r="L229" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41944.531257280018</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.3">
@@ -9520,9 +9534,9 @@
       <c r="K230" t="s">
         <v>33</v>
       </c>
-      <c r="L230" s="2" t="e">
+      <c r="L230" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41613.012011414772</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.3">
@@ -9559,9 +9573,9 @@
       <c r="K231" t="s">
         <v>26</v>
       </c>
-      <c r="L231" s="2" t="e">
+      <c r="L231" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42080.034302474945</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.3">
@@ -9598,9 +9612,9 @@
       <c r="K232" t="s">
         <v>14</v>
       </c>
-      <c r="L232" s="2" t="e">
+      <c r="L232" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40804.350002344283</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.3">
@@ -9637,9 +9651,9 @@
       <c r="K233" t="s">
         <v>20</v>
       </c>
-      <c r="L233" s="2" t="e">
+      <c r="L233" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41596.553440212614</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.3">
@@ -9676,9 +9690,9 @@
       <c r="K234" t="s">
         <v>20</v>
       </c>
-      <c r="L234" s="2" t="e">
+      <c r="L234" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41766.888293568969</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.3">
@@ -9715,9 +9729,9 @@
       <c r="K235" t="s">
         <v>37</v>
       </c>
-      <c r="L235" s="2" t="e">
+      <c r="L235" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40835.762332368962</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.3">
@@ -9754,9 +9768,9 @@
       <c r="K236" t="s">
         <v>14</v>
       </c>
-      <c r="L236" s="2" t="e">
+      <c r="L236" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40694.211738922742</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.3">
@@ -9793,9 +9807,9 @@
       <c r="K237" t="s">
         <v>23</v>
       </c>
-      <c r="L237" s="2" t="e">
+      <c r="L237" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40737.962802059141</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.3">
@@ -9832,9 +9846,9 @@
       <c r="K238" t="s">
         <v>17</v>
       </c>
-      <c r="L238" s="2" t="e">
+      <c r="L238" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41316.530159634072</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.3">
@@ -9871,9 +9885,9 @@
       <c r="K239" t="s">
         <v>17</v>
       </c>
-      <c r="L239" s="2" t="e">
+      <c r="L239" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40856.764999664636</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.3">
@@ -9910,9 +9924,9 @@
       <c r="K240" t="s">
         <v>17</v>
       </c>
-      <c r="L240" s="2" t="e">
+      <c r="L240" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40206.621080335462</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.3">
@@ -9949,9 +9963,9 @@
       <c r="K241" t="s">
         <v>20</v>
       </c>
-      <c r="L241" s="2" t="e">
+      <c r="L241" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42160.796092890334</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.3">
@@ -9988,9 +10002,9 @@
       <c r="K242" t="s">
         <v>17</v>
       </c>
-      <c r="L242" s="2" t="e">
+      <c r="L242" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41248.060840882688</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.3">
@@ -10027,9 +10041,9 @@
       <c r="K243" t="s">
         <v>37</v>
       </c>
-      <c r="L243" s="2" t="e">
+      <c r="L243" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41197.514565116442</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.3">
@@ -10066,9 +10080,9 @@
       <c r="K244" t="s">
         <v>29</v>
       </c>
-      <c r="L244" s="2" t="e">
+      <c r="L244" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41642.969899439529</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.3">
@@ -10105,9 +10119,9 @@
       <c r="K245" t="s">
         <v>23</v>
       </c>
-      <c r="L245" s="2" t="e">
+      <c r="L245" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41646.467626719335</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.3">
@@ -10144,9 +10158,9 @@
       <c r="K246" t="s">
         <v>26</v>
       </c>
-      <c r="L246" s="2" t="e">
+      <c r="L246" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>42138.461656047955</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.3">
@@ -10183,9 +10197,9 @@
       <c r="K247" t="s">
         <v>33</v>
       </c>
-      <c r="L247" s="2" t="e">
+      <c r="L247" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40996.177879555493</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.3">
@@ -10222,9 +10236,9 @@
       <c r="K248" t="s">
         <v>33</v>
       </c>
-      <c r="L248" s="2" t="e">
+      <c r="L248" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41298.599434257048</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.3">
@@ -10261,9 +10275,9 @@
       <c r="K249" t="s">
         <v>20</v>
       </c>
-      <c r="L249" s="2" t="e">
+      <c r="L249" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41263.31628807274</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.3">
@@ -10300,9 +10314,9 @@
       <c r="K250" t="s">
         <v>14</v>
       </c>
-      <c r="L250" s="2" t="e">
+      <c r="L250" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40615.572260099158</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.3">
@@ -10339,9 +10353,9 @@
       <c r="K251" t="s">
         <v>20</v>
       </c>
-      <c r="L251" s="2" t="e">
+      <c r="L251" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40328.644055880759</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.3">
@@ -10378,9 +10392,9 @@
       <c r="K252" t="s">
         <v>29</v>
       </c>
-      <c r="L252" s="2" t="e">
+      <c r="L252" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40785.472708797548</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.3">
@@ -10417,9 +10431,9 @@
       <c r="K253" t="s">
         <v>26</v>
       </c>
-      <c r="L253" s="2" t="e">
+      <c r="L253" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41641.01807646524</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.3">
@@ -10456,9 +10470,9 @@
       <c r="K254" t="s">
         <v>20</v>
       </c>
-      <c r="L254" s="2" t="e">
+      <c r="L254" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40627.786368982037</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.3">
@@ -10495,9 +10509,9 @@
       <c r="K255" t="s">
         <v>29</v>
       </c>
-      <c r="L255" s="2" t="e">
+      <c r="L255" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41564.617872342751</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.3">
@@ -10534,9 +10548,9 @@
       <c r="K256" t="s">
         <v>17</v>
       </c>
-      <c r="L256" s="2" t="e">
+      <c r="L256" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41620.375178253998</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
@@ -10573,9 +10587,9 @@
       <c r="K257" t="s">
         <v>26</v>
       </c>
-      <c r="L257" s="2" t="e">
+      <c r="L257" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>41493.425254238624</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
@@ -10612,9 +10626,9 @@
       <c r="K258" t="s">
         <v>26</v>
       </c>
-      <c r="L258" s="2" t="e">
+      <c r="L258" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>#VALUE!</v>
+        <v>40333.600556584155</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
@@ -10651,9 +10665,9 @@
       <c r="K259" t="s">
         <v>37</v>
       </c>
-      <c r="L259" s="2" t="e">
+      <c r="L259" s="2">
         <f t="shared" ref="L259:L322" ca="1" si="4">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>40238.276449461402</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
@@ -10690,9 +10704,9 @@
       <c r="K260" t="s">
         <v>29</v>
       </c>
-      <c r="L260" s="2" t="e">
+      <c r="L260" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41223.21251248919</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
@@ -10729,9 +10743,9 @@
       <c r="K261" t="s">
         <v>20</v>
       </c>
-      <c r="L261" s="2" t="e">
+      <c r="L261" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41765.938046028605</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
@@ -10768,9 +10782,9 @@
       <c r="K262" t="s">
         <v>54</v>
       </c>
-      <c r="L262" s="2" t="e">
+      <c r="L262" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40887.505778455503</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
@@ -10807,9 +10821,9 @@
       <c r="K263" t="s">
         <v>20</v>
       </c>
-      <c r="L263" s="2" t="e">
+      <c r="L263" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40645.577589930232</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
@@ -10846,9 +10860,9 @@
       <c r="K264" t="s">
         <v>23</v>
       </c>
-      <c r="L264" s="2" t="e">
+      <c r="L264" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41136.465050436527</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
@@ -10885,9 +10899,9 @@
       <c r="K265" t="s">
         <v>14</v>
       </c>
-      <c r="L265" s="2" t="e">
+      <c r="L265" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41372.372910770559</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
@@ -10924,9 +10938,9 @@
       <c r="K266" t="s">
         <v>20</v>
       </c>
-      <c r="L266" s="2" t="e">
+      <c r="L266" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40611.836519588585</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
@@ -10963,9 +10977,9 @@
       <c r="K267" t="s">
         <v>29</v>
       </c>
-      <c r="L267" s="2" t="e">
+      <c r="L267" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41881.208885029402</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
@@ -11002,9 +11016,9 @@
       <c r="K268" t="s">
         <v>33</v>
       </c>
-      <c r="L268" s="2" t="e">
+      <c r="L268" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41661.816440466537</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
@@ -11041,9 +11055,9 @@
       <c r="K269" t="s">
         <v>29</v>
       </c>
-      <c r="L269" s="2" t="e">
+      <c r="L269" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41266.33120296237</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
@@ -11080,9 +11094,9 @@
       <c r="K270" t="s">
         <v>17</v>
       </c>
-      <c r="L270" s="2" t="e">
+      <c r="L270" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41771.965686248048</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
@@ -11119,9 +11133,9 @@
       <c r="K271" t="s">
         <v>33</v>
       </c>
-      <c r="L271" s="2" t="e">
+      <c r="L271" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40883.891562901023</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
@@ -11158,9 +11172,9 @@
       <c r="K272" t="s">
         <v>31</v>
       </c>
-      <c r="L272" s="2" t="e">
+      <c r="L272" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40736.144500226757</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.3">
@@ -11197,9 +11211,9 @@
       <c r="K273" t="s">
         <v>31</v>
       </c>
-      <c r="L273" s="2" t="e">
+      <c r="L273" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40947.282325471308</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.3">
@@ -11236,9 +11250,9 @@
       <c r="K274" t="s">
         <v>54</v>
       </c>
-      <c r="L274" s="2" t="e">
+      <c r="L274" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42144.091228781028</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.3">
@@ -11275,9 +11289,9 @@
       <c r="K275" t="s">
         <v>31</v>
       </c>
-      <c r="L275" s="2" t="e">
+      <c r="L275" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40350.196662140843</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.3">
@@ -11314,9 +11328,9 @@
       <c r="K276" t="s">
         <v>14</v>
       </c>
-      <c r="L276" s="2" t="e">
+      <c r="L276" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41787.631897081643</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.3">
@@ -11353,9 +11367,9 @@
       <c r="K277" t="s">
         <v>31</v>
       </c>
-      <c r="L277" s="2" t="e">
+      <c r="L277" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41232.913755915106</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.3">
@@ -11392,9 +11406,9 @@
       <c r="K278" t="s">
         <v>20</v>
       </c>
-      <c r="L278" s="2" t="e">
+      <c r="L278" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41993.114215173431</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.3">
@@ -11431,9 +11445,9 @@
       <c r="K279" t="s">
         <v>23</v>
       </c>
-      <c r="L279" s="2" t="e">
+      <c r="L279" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40696.295648806634</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.3">
@@ -11470,9 +11484,9 @@
       <c r="K280" t="s">
         <v>17</v>
       </c>
-      <c r="L280" s="2" t="e">
+      <c r="L280" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40936.877981387457</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.3">
@@ -11509,9 +11523,9 @@
       <c r="K281" t="s">
         <v>37</v>
       </c>
-      <c r="L281" s="2" t="e">
+      <c r="L281" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42009.745972722776</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.3">
@@ -11548,9 +11562,9 @@
       <c r="K282" t="s">
         <v>29</v>
       </c>
-      <c r="L282" s="2" t="e">
+      <c r="L282" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42275.491265712939</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.3">
@@ -11587,9 +11601,9 @@
       <c r="K283" t="s">
         <v>29</v>
       </c>
-      <c r="L283" s="2" t="e">
+      <c r="L283" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41391.161562224508</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.3">
@@ -11626,9 +11640,9 @@
       <c r="K284" t="s">
         <v>20</v>
       </c>
-      <c r="L284" s="2" t="e">
+      <c r="L284" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40998.133451682203</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.3">
@@ -11665,9 +11679,9 @@
       <c r="K285" t="s">
         <v>17</v>
       </c>
-      <c r="L285" s="2" t="e">
+      <c r="L285" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42292.52189512358</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.3">
@@ -11704,9 +11718,9 @@
       <c r="K286" t="s">
         <v>17</v>
       </c>
-      <c r="L286" s="2" t="e">
+      <c r="L286" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40759.128735286955</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.3">
@@ -11743,9 +11757,9 @@
       <c r="K287" t="s">
         <v>26</v>
       </c>
-      <c r="L287" s="2" t="e">
+      <c r="L287" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40742.334143412561</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.3">
@@ -11782,9 +11796,9 @@
       <c r="K288" t="s">
         <v>17</v>
       </c>
-      <c r="L288" s="2" t="e">
+      <c r="L288" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41231.839792313265</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.3">
@@ -11821,9 +11835,9 @@
       <c r="K289" t="s">
         <v>20</v>
       </c>
-      <c r="L289" s="2" t="e">
+      <c r="L289" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41624.568328498957</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.3">
@@ -11860,9 +11874,9 @@
       <c r="K290" t="s">
         <v>29</v>
       </c>
-      <c r="L290" s="2" t="e">
+      <c r="L290" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41823.520813883915</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.3">
@@ -11899,9 +11913,9 @@
       <c r="K291" t="s">
         <v>37</v>
       </c>
-      <c r="L291" s="2" t="e">
+      <c r="L291" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40648.10864434488</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.3">
@@ -11938,9 +11952,9 @@
       <c r="K292" t="s">
         <v>31</v>
       </c>
-      <c r="L292" s="2" t="e">
+      <c r="L292" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41703.441200527268</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.3">
@@ -11977,9 +11991,9 @@
       <c r="K293" t="s">
         <v>37</v>
       </c>
-      <c r="L293" s="2" t="e">
+      <c r="L293" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42234.79876068922</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.3">
@@ -12016,9 +12030,9 @@
       <c r="K294" t="s">
         <v>14</v>
       </c>
-      <c r="L294" s="2" t="e">
+      <c r="L294" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41641.922933290669</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.3">
@@ -12055,9 +12069,9 @@
       <c r="K295" t="s">
         <v>33</v>
       </c>
-      <c r="L295" s="2" t="e">
+      <c r="L295" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41901.235845510397</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.3">
@@ -12094,9 +12108,9 @@
       <c r="K296" t="s">
         <v>20</v>
       </c>
-      <c r="L296" s="2" t="e">
+      <c r="L296" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40428.066844551868</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.3">
@@ -12133,9 +12147,9 @@
       <c r="K297" t="s">
         <v>54</v>
       </c>
-      <c r="L297" s="2" t="e">
+      <c r="L297" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42132.975319655248</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.3">
@@ -12172,9 +12186,9 @@
       <c r="K298" t="s">
         <v>29</v>
       </c>
-      <c r="L298" s="2" t="e">
+      <c r="L298" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40900.82633412398</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.3">
@@ -12211,9 +12225,9 @@
       <c r="K299" t="s">
         <v>14</v>
       </c>
-      <c r="L299" s="2" t="e">
+      <c r="L299" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40828.391787238113</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.3">
@@ -12250,9 +12264,9 @@
       <c r="K300" t="s">
         <v>23</v>
       </c>
-      <c r="L300" s="2" t="e">
+      <c r="L300" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41814.158362961236</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.3">
@@ -12289,9 +12303,9 @@
       <c r="K301" t="s">
         <v>14</v>
       </c>
-      <c r="L301" s="2" t="e">
+      <c r="L301" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41401.808068335857</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.3">
@@ -12328,9 +12342,9 @@
       <c r="K302" t="s">
         <v>23</v>
       </c>
-      <c r="L302" s="2" t="e">
+      <c r="L302" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42138.258824905548</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.3">
@@ -12367,9 +12381,9 @@
       <c r="K303" t="s">
         <v>14</v>
       </c>
-      <c r="L303" s="2" t="e">
+      <c r="L303" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41394.554450238997</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.3">
@@ -12406,9 +12420,9 @@
       <c r="K304" t="s">
         <v>26</v>
       </c>
-      <c r="L304" s="2" t="e">
+      <c r="L304" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41184.519461868302</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.3">
@@ -12445,9 +12459,9 @@
       <c r="K305" t="s">
         <v>14</v>
       </c>
-      <c r="L305" s="2" t="e">
+      <c r="L305" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41862.436879567373</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.3">
@@ -12484,9 +12498,9 @@
       <c r="K306" t="s">
         <v>37</v>
       </c>
-      <c r="L306" s="2" t="e">
+      <c r="L306" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40882.919408218011</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.3">
@@ -12523,9 +12537,9 @@
       <c r="K307" t="s">
         <v>54</v>
       </c>
-      <c r="L307" s="2" t="e">
+      <c r="L307" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40967.91410411847</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.3">
@@ -12562,9 +12576,9 @@
       <c r="K308" t="s">
         <v>26</v>
       </c>
-      <c r="L308" s="2" t="e">
+      <c r="L308" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42119.627030545322</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.3">
@@ -12601,9 +12615,9 @@
       <c r="K309" t="s">
         <v>29</v>
       </c>
-      <c r="L309" s="2" t="e">
+      <c r="L309" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42327.619497548825</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.3">
@@ -12640,9 +12654,9 @@
       <c r="K310" t="s">
         <v>54</v>
       </c>
-      <c r="L310" s="2" t="e">
+      <c r="L310" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40379.754839737601</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.3">
@@ -12679,9 +12693,9 @@
       <c r="K311" t="s">
         <v>20</v>
       </c>
-      <c r="L311" s="2" t="e">
+      <c r="L311" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40218.765324932385</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.3">
@@ -12718,9 +12732,9 @@
       <c r="K312" t="s">
         <v>54</v>
       </c>
-      <c r="L312" s="2" t="e">
+      <c r="L312" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41117.995550210857</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.3">
@@ -12757,9 +12771,9 @@
       <c r="K313" t="s">
         <v>33</v>
       </c>
-      <c r="L313" s="2" t="e">
+      <c r="L313" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41836.10048262772</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.3">
@@ -12796,9 +12810,9 @@
       <c r="K314" t="s">
         <v>29</v>
       </c>
-      <c r="L314" s="2" t="e">
+      <c r="L314" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42371.93562276203</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.3">
@@ -12835,9 +12849,9 @@
       <c r="K315" t="s">
         <v>29</v>
       </c>
-      <c r="L315" s="2" t="e">
+      <c r="L315" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40546.428573377438</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.3">
@@ -12874,9 +12888,9 @@
       <c r="K316" t="s">
         <v>20</v>
       </c>
-      <c r="L316" s="2" t="e">
+      <c r="L316" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41237.769950560149</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.3">
@@ -12913,9 +12927,9 @@
       <c r="K317" t="s">
         <v>31</v>
       </c>
-      <c r="L317" s="2" t="e">
+      <c r="L317" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42269.219058314331</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.3">
@@ -12952,9 +12966,9 @@
       <c r="K318" t="s">
         <v>20</v>
       </c>
-      <c r="L318" s="2" t="e">
+      <c r="L318" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41539.616983834443</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.3">
@@ -12991,9 +13005,9 @@
       <c r="K319" t="s">
         <v>20</v>
       </c>
-      <c r="L319" s="2" t="e">
+      <c r="L319" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40544.411112546812</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.3">
@@ -13030,9 +13044,9 @@
       <c r="K320" t="s">
         <v>29</v>
       </c>
-      <c r="L320" s="2" t="e">
+      <c r="L320" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>41577.086151486888</v>
       </c>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.3">
@@ -13069,9 +13083,9 @@
       <c r="K321" t="s">
         <v>31</v>
       </c>
-      <c r="L321" s="2" t="e">
+      <c r="L321" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>40817.529975565863</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.3">
@@ -13108,9 +13122,9 @@
       <c r="K322" t="s">
         <v>54</v>
       </c>
-      <c r="L322" s="2" t="e">
+      <c r="L322" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>#VALUE!</v>
+        <v>42308.040706233929</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.3">
@@ -13147,9 +13161,9 @@
       <c r="K323" t="s">
         <v>17</v>
       </c>
-      <c r="L323" s="2" t="e">
+      <c r="L323" s="2">
         <f t="shared" ref="L323:L386" ca="1" si="5">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41855.697202732656</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.3">
@@ -13186,9 +13200,9 @@
       <c r="K324" t="s">
         <v>29</v>
       </c>
-      <c r="L324" s="2" t="e">
+      <c r="L324" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41717.813563062628</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.3">
@@ -13225,9 +13239,9 @@
       <c r="K325" t="s">
         <v>33</v>
       </c>
-      <c r="L325" s="2" t="e">
+      <c r="L325" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41344.40363458357</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.3">
@@ -13264,9 +13278,9 @@
       <c r="K326" t="s">
         <v>23</v>
       </c>
-      <c r="L326" s="2" t="e">
+      <c r="L326" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41237.13627789358</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.3">
@@ -13303,9 +13317,9 @@
       <c r="K327" t="s">
         <v>23</v>
       </c>
-      <c r="L327" s="2" t="e">
+      <c r="L327" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41376.805471208936</v>
       </c>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.3">
@@ -13342,9 +13356,9 @@
       <c r="K328" t="s">
         <v>14</v>
       </c>
-      <c r="L328" s="2" t="e">
+      <c r="L328" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41122.646333779565</v>
       </c>
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.3">
@@ -13381,9 +13395,9 @@
       <c r="K329" t="s">
         <v>23</v>
       </c>
-      <c r="L329" s="2" t="e">
+      <c r="L329" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41098.386304146203</v>
       </c>
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.3">
@@ -13420,9 +13434,9 @@
       <c r="K330" t="s">
         <v>31</v>
       </c>
-      <c r="L330" s="2" t="e">
+      <c r="L330" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42230.268366498647</v>
       </c>
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.3">
@@ -13459,9 +13473,9 @@
       <c r="K331" t="s">
         <v>29</v>
       </c>
-      <c r="L331" s="2" t="e">
+      <c r="L331" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42201.104977426083</v>
       </c>
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.3">
@@ -13498,9 +13512,9 @@
       <c r="K332" t="s">
         <v>33</v>
       </c>
-      <c r="L332" s="2" t="e">
+      <c r="L332" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42054.503816712451</v>
       </c>
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.3">
@@ -13537,9 +13551,9 @@
       <c r="K333" t="s">
         <v>20</v>
       </c>
-      <c r="L333" s="2" t="e">
+      <c r="L333" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41305.962166625955</v>
       </c>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.3">
@@ -13576,9 +13590,9 @@
       <c r="K334" t="s">
         <v>33</v>
       </c>
-      <c r="L334" s="2" t="e">
+      <c r="L334" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41931.707078876541</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.3">
@@ -13615,9 +13629,9 @@
       <c r="K335" t="s">
         <v>37</v>
       </c>
-      <c r="L335" s="2" t="e">
+      <c r="L335" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41758.025882339083</v>
       </c>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.3">
@@ -13654,9 +13668,9 @@
       <c r="K336" t="s">
         <v>29</v>
       </c>
-      <c r="L336" s="2" t="e">
+      <c r="L336" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41830.387709945906</v>
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.3">
@@ -13693,9 +13707,9 @@
       <c r="K337" t="s">
         <v>37</v>
       </c>
-      <c r="L337" s="2" t="e">
+      <c r="L337" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41036.368239560994</v>
       </c>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.3">
@@ -13732,9 +13746,9 @@
       <c r="K338" t="s">
         <v>26</v>
       </c>
-      <c r="L338" s="2" t="e">
+      <c r="L338" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40682.475022732411</v>
       </c>
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.3">
@@ -13771,9 +13785,9 @@
       <c r="K339" t="s">
         <v>31</v>
       </c>
-      <c r="L339" s="2" t="e">
+      <c r="L339" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41632.771899274674</v>
       </c>
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.3">
@@ -13810,9 +13824,9 @@
       <c r="K340" t="s">
         <v>31</v>
       </c>
-      <c r="L340" s="2" t="e">
+      <c r="L340" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42190.508323084003</v>
       </c>
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.3">
@@ -13849,9 +13863,9 @@
       <c r="K341" t="s">
         <v>26</v>
       </c>
-      <c r="L341" s="2" t="e">
+      <c r="L341" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40353.724897176406</v>
       </c>
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.3">
@@ -13888,9 +13902,9 @@
       <c r="K342" t="s">
         <v>31</v>
       </c>
-      <c r="L342" s="2" t="e">
+      <c r="L342" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42044.390488650613</v>
       </c>
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.3">
@@ -13927,9 +13941,9 @@
       <c r="K343" t="s">
         <v>31</v>
       </c>
-      <c r="L343" s="2" t="e">
+      <c r="L343" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41143.562809457275</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.3">
@@ -13966,9 +13980,9 @@
       <c r="K344" t="s">
         <v>37</v>
       </c>
-      <c r="L344" s="2" t="e">
+      <c r="L344" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40580.319147057817</v>
       </c>
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.3">
@@ -14005,9 +14019,9 @@
       <c r="K345" t="s">
         <v>33</v>
       </c>
-      <c r="L345" s="2" t="e">
+      <c r="L345" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40999.188581451148</v>
       </c>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.3">
@@ -14044,9 +14058,9 @@
       <c r="K346" t="s">
         <v>20</v>
       </c>
-      <c r="L346" s="2" t="e">
+      <c r="L346" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41264.419086971575</v>
       </c>
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.3">
@@ -14083,9 +14097,9 @@
       <c r="K347" t="s">
         <v>20</v>
       </c>
-      <c r="L347" s="2" t="e">
+      <c r="L347" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42208.961429621231</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.3">
@@ -14122,9 +14136,9 @@
       <c r="K348" t="s">
         <v>17</v>
       </c>
-      <c r="L348" s="2" t="e">
+      <c r="L348" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41512.948965883872</v>
       </c>
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.3">
@@ -14161,9 +14175,9 @@
       <c r="K349" t="s">
         <v>26</v>
       </c>
-      <c r="L349" s="2" t="e">
+      <c r="L349" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41856.879886762799</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.3">
@@ -14200,9 +14214,9 @@
       <c r="K350" t="s">
         <v>20</v>
       </c>
-      <c r="L350" s="2" t="e">
+      <c r="L350" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41573.746453341031</v>
       </c>
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.3">
@@ -14239,9 +14253,9 @@
       <c r="K351" t="s">
         <v>31</v>
       </c>
-      <c r="L351" s="2" t="e">
+      <c r="L351" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41391.338813571478</v>
       </c>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.3">
@@ -14278,9 +14292,9 @@
       <c r="K352" t="s">
         <v>17</v>
       </c>
-      <c r="L352" s="2" t="e">
+      <c r="L352" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41151.237917142171</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.3">
@@ -14317,9 +14331,9 @@
       <c r="K353" t="s">
         <v>37</v>
       </c>
-      <c r="L353" s="2" t="e">
+      <c r="L353" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40333.721110970808</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.3">
@@ -14356,9 +14370,9 @@
       <c r="K354" t="s">
         <v>29</v>
       </c>
-      <c r="L354" s="2" t="e">
+      <c r="L354" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40224.751498889847</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.3">
@@ -14395,9 +14409,9 @@
       <c r="K355" t="s">
         <v>20</v>
       </c>
-      <c r="L355" s="2" t="e">
+      <c r="L355" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41939.479468064208</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.3">
@@ -14434,9 +14448,9 @@
       <c r="K356" t="s">
         <v>14</v>
       </c>
-      <c r="L356" s="2" t="e">
+      <c r="L356" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41464.440702114152</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.3">
@@ -14473,9 +14487,9 @@
       <c r="K357" t="s">
         <v>54</v>
       </c>
-      <c r="L357" s="2" t="e">
+      <c r="L357" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42274.509510249234</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.3">
@@ -14512,9 +14526,9 @@
       <c r="K358" t="s">
         <v>23</v>
       </c>
-      <c r="L358" s="2" t="e">
+      <c r="L358" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40807.810808444505</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.3">
@@ -14551,9 +14565,9 @@
       <c r="K359" t="s">
         <v>33</v>
       </c>
-      <c r="L359" s="2" t="e">
+      <c r="L359" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40530.341367214736</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.3">
@@ -14590,9 +14604,9 @@
       <c r="K360" t="s">
         <v>37</v>
       </c>
-      <c r="L360" s="2" t="e">
+      <c r="L360" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41658.811513775996</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.3">
@@ -14629,9 +14643,9 @@
       <c r="K361" t="s">
         <v>26</v>
       </c>
-      <c r="L361" s="2" t="e">
+      <c r="L361" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40515.379856012609</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.3">
@@ -14668,9 +14682,9 @@
       <c r="K362" t="s">
         <v>33</v>
       </c>
-      <c r="L362" s="2" t="e">
+      <c r="L362" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40665.365528265655</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.3">
@@ -14707,9 +14721,9 @@
       <c r="K363" t="s">
         <v>20</v>
       </c>
-      <c r="L363" s="2" t="e">
+      <c r="L363" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41024.622225731029</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.3">
@@ -14746,9 +14760,9 @@
       <c r="K364" t="s">
         <v>54</v>
       </c>
-      <c r="L364" s="2" t="e">
+      <c r="L364" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41407.859726653216</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.3">
@@ -14785,9 +14799,9 @@
       <c r="K365" t="s">
         <v>14</v>
       </c>
-      <c r="L365" s="2" t="e">
+      <c r="L365" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41703.731041803039</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.3">
@@ -14824,9 +14838,9 @@
       <c r="K366" t="s">
         <v>26</v>
       </c>
-      <c r="L366" s="2" t="e">
+      <c r="L366" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41663.007056973911</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.3">
@@ -14863,9 +14877,9 @@
       <c r="K367" t="s">
         <v>33</v>
       </c>
-      <c r="L367" s="2" t="e">
+      <c r="L367" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41346.286875851983</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.3">
@@ -14902,9 +14916,9 @@
       <c r="K368" t="s">
         <v>54</v>
       </c>
-      <c r="L368" s="2" t="e">
+      <c r="L368" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41266.652348567892</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.3">
@@ -14941,9 +14955,9 @@
       <c r="K369" t="s">
         <v>33</v>
       </c>
-      <c r="L369" s="2" t="e">
+      <c r="L369" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40883.604799310153</v>
       </c>
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.3">
@@ -14980,9 +14994,9 @@
       <c r="K370" t="s">
         <v>33</v>
       </c>
-      <c r="L370" s="2" t="e">
+      <c r="L370" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41333.918318447686</v>
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.3">
@@ -15019,9 +15033,9 @@
       <c r="K371" t="s">
         <v>23</v>
       </c>
-      <c r="L371" s="2" t="e">
+      <c r="L371" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40491.146717945761</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.3">
@@ -15058,9 +15072,9 @@
       <c r="K372" t="s">
         <v>37</v>
       </c>
-      <c r="L372" s="2" t="e">
+      <c r="L372" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41521.159825837691</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.3">
@@ -15097,9 +15111,9 @@
       <c r="K373" t="s">
         <v>26</v>
       </c>
-      <c r="L373" s="2" t="e">
+      <c r="L373" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42076.279337050008</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.3">
@@ -15136,9 +15150,9 @@
       <c r="K374" t="s">
         <v>31</v>
       </c>
-      <c r="L374" s="2" t="e">
+      <c r="L374" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42360.24315105001</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.3">
@@ -15175,9 +15189,9 @@
       <c r="K375" t="s">
         <v>29</v>
       </c>
-      <c r="L375" s="2" t="e">
+      <c r="L375" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41579.457309271871</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.3">
@@ -15214,9 +15228,9 @@
       <c r="K376" t="s">
         <v>33</v>
       </c>
-      <c r="L376" s="2" t="e">
+      <c r="L376" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42212.180486791818</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.3">
@@ -15253,9 +15267,9 @@
       <c r="K377" t="s">
         <v>33</v>
       </c>
-      <c r="L377" s="2" t="e">
+      <c r="L377" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40423.120780499834</v>
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.3">
@@ -15292,9 +15306,9 @@
       <c r="K378" t="s">
         <v>20</v>
       </c>
-      <c r="L378" s="2" t="e">
+      <c r="L378" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41665.464433854584</v>
       </c>
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.3">
@@ -15331,9 +15345,9 @@
       <c r="K379" t="s">
         <v>23</v>
       </c>
-      <c r="L379" s="2" t="e">
+      <c r="L379" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41899.494607102562</v>
       </c>
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.3">
@@ -15370,9 +15384,9 @@
       <c r="K380" t="s">
         <v>37</v>
       </c>
-      <c r="L380" s="2" t="e">
+      <c r="L380" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41012.992846983885</v>
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.3">
@@ -15409,9 +15423,9 @@
       <c r="K381" t="s">
         <v>20</v>
       </c>
-      <c r="L381" s="2" t="e">
+      <c r="L381" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40553.380993462277</v>
       </c>
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.3">
@@ -15448,9 +15462,9 @@
       <c r="K382" t="s">
         <v>20</v>
       </c>
-      <c r="L382" s="2" t="e">
+      <c r="L382" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41034.895887739382</v>
       </c>
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.3">
@@ -15487,9 +15501,9 @@
       <c r="K383" t="s">
         <v>26</v>
       </c>
-      <c r="L383" s="2" t="e">
+      <c r="L383" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>40354.542405418098</v>
       </c>
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.3">
@@ -15526,9 +15540,9 @@
       <c r="K384" t="s">
         <v>23</v>
       </c>
-      <c r="L384" s="2" t="e">
+      <c r="L384" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41480.614330221251</v>
       </c>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.3">
@@ -15565,9 +15579,9 @@
       <c r="K385" t="s">
         <v>23</v>
       </c>
-      <c r="L385" s="2" t="e">
+      <c r="L385" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>41118.496384254773</v>
       </c>
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.3">
@@ -15604,9 +15618,9 @@
       <c r="K386" t="s">
         <v>31</v>
       </c>
-      <c r="L386" s="2" t="e">
+      <c r="L386" s="2">
         <f t="shared" ca="1" si="5"/>
-        <v>#VALUE!</v>
+        <v>42188.632803466833</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.3">
@@ -15643,9 +15657,9 @@
       <c r="K387" t="s">
         <v>23</v>
       </c>
-      <c r="L387" s="2" t="e">
+      <c r="L387" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41557.209772288872</v>
       </c>
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.3">
@@ -15682,9 +15696,9 @@
       <c r="K388" t="s">
         <v>17</v>
       </c>
-      <c r="L388" s="2" t="e">
+      <c r="L388" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>42085.931602973222</v>
       </c>
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.3">
@@ -15721,9 +15735,9 @@
       <c r="K389" t="s">
         <v>14</v>
       </c>
-      <c r="L389" s="2" t="e">
+      <c r="L389" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>42032.359190364092</v>
       </c>
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.3">
@@ -15760,9 +15774,9 @@
       <c r="K390" t="s">
         <v>33</v>
       </c>
-      <c r="L390" s="2" t="e">
+      <c r="L390" s="2">
         <f ca="1">(RAND()*("14/01/2016"-"14/01/2010"+1))+"14/01/2010"</f>
-        <v>#VALUE!</v>
+        <v>41985.075475968981</v>
       </c>
     </row>
   </sheetData>
